--- a/data/trans_orig/P16-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2007</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>598408</t>
+          <t>597178</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>660548</t>
+          <t>662995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>975644</t>
+          <t>974874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1034228</t>
+          <t>1033469</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1588408</t>
+          <t>1590292</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1679379</t>
+          <t>1678361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>371175</t>
+          <t>368728</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433315</t>
+          <t>434545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280885</t>
+          <t>281644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339469</t>
+          <t>340239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>667456</t>
+          <t>668474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>758427</t>
+          <t>756543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>478318</t>
+          <t>477504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>551333</t>
+          <t>555246</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>694465</t>
+          <t>693674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>773338</t>
+          <t>768611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1188890</t>
+          <t>1194029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1298650</t>
+          <t>1301060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1141061</t>
+          <t>1137148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1214076</t>
+          <t>1214890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>814335</t>
+          <t>819062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>893208</t>
+          <t>893999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1981417</t>
+          <t>1979007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2091177</t>
+          <t>2086038</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>162139</t>
+          <t>160663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>208621</t>
+          <t>208657</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>219501</t>
+          <t>218835</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>264011</t>
+          <t>264951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>395253</t>
+          <t>394751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>459125</t>
+          <t>459950</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>342787</t>
+          <t>342751</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>389269</t>
+          <t>390745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>212401</t>
+          <t>211461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256911</t>
+          <t>257577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>568695</t>
+          <t>567870</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632567</t>
+          <t>633069</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1273254</t>
+          <t>1278406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1384974</t>
+          <t>1386547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1917351</t>
+          <t>1921725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2039467</t>
+          <t>2034112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3224177</t>
+          <t>3225281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3385897</t>
+          <t>3389671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1890551</t>
+          <t>1888978</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2002271</t>
+          <t>1997119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1339730</t>
+          <t>1345085</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1461846</t>
+          <t>1457472</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3268825</t>
+          <t>3265051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3430545</t>
+          <t>3429441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2012</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2012 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>669162</t>
+          <t>671507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>727562</t>
+          <t>729654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1108998</t>
+          <t>1107467</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1162473</t>
+          <t>1163494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1797326</t>
+          <t>1795143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1877711</t>
+          <t>1876562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>247081</t>
+          <t>244989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305481</t>
+          <t>303136</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>174289</t>
+          <t>173268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227764</t>
+          <t>229295</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>433694</t>
+          <t>434843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>514079</t>
+          <t>516262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>780841</t>
+          <t>783376</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>871150</t>
+          <t>874365</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1041960</t>
+          <t>1046632</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1128714</t>
+          <t>1129406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1848353</t>
+          <t>1848054</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1982196</t>
+          <t>1974775</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1088872</t>
+          <t>1085657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1179181</t>
+          <t>1176646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>628198</t>
+          <t>627506</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>714952</t>
+          <t>710280</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1734738</t>
+          <t>1742159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1868581</t>
+          <t>1868880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173448</t>
+          <t>172597</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>218571</t>
+          <t>220344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>244143</t>
+          <t>244726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>293457</t>
+          <t>290156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>433495</t>
+          <t>430680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>500288</t>
+          <t>497132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,0%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>261761</t>
+          <t>259988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306884</t>
+          <t>307735</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164197</t>
+          <t>167498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>213511</t>
+          <t>212928</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>437698</t>
+          <t>440854</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>504491</t>
+          <t>507306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1661440</t>
+          <t>1662857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1779309</t>
+          <t>1786307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2437612</t>
+          <t>2433442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2544992</t>
+          <t>2543822</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4120844</t>
+          <t>4129939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4295376</t>
+          <t>4295748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1635688</t>
+          <t>1628690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1753557</t>
+          <t>1752140</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1006337</t>
+          <t>1007507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1113717</t>
+          <t>1117887</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2670950</t>
+          <t>2670578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2845482</t>
+          <t>2836387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2016</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>489578</t>
+          <t>488256</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>540583</t>
+          <t>540180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>817229</t>
+          <t>817366</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>862855</t>
+          <t>862630</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1319492</t>
+          <t>1318528</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1388677</t>
+          <t>1390542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>213764</t>
+          <t>214167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264769</t>
+          <t>266091</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131805</t>
+          <t>132030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>177431</t>
+          <t>177294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>360330</t>
+          <t>358465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>429515</t>
+          <t>430479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>872240</t>
+          <t>873312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>961316</t>
+          <t>962683</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1100770</t>
+          <t>1101753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1191156</t>
+          <t>1192191</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1995699</t>
+          <t>2001357</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2126387</t>
+          <t>2128457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1115069</t>
+          <t>1113702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1204145</t>
+          <t>1203073</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>797144</t>
+          <t>796109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>887530</t>
+          <t>886547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1938298</t>
+          <t>1936228</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2068986</t>
+          <t>2063328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,76%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>222028</t>
+          <t>221990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>271009</t>
+          <t>271282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>279659</t>
+          <t>278616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>326371</t>
+          <t>324989</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>510426</t>
+          <t>513069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>581194</t>
+          <t>578269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,76%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275877</t>
+          <t>275604</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324858</t>
+          <t>324896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222769</t>
+          <t>224151</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269481</t>
+          <t>270524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>514833</t>
+          <t>517758</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>585601</t>
+          <t>582958</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,19%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1616497</t>
+          <t>1613679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1737528</t>
+          <t>1736973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2234206</t>
+          <t>2231949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2346384</t>
+          <t>2348766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3879500</t>
+          <t>3889010</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4057962</t>
+          <t>4051138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1640090</t>
+          <t>1640645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1761121</t>
+          <t>1763939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1185716</t>
+          <t>1183334</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1297894</t>
+          <t>1300151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2851756</t>
+          <t>2858580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3030218</t>
+          <t>3020708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2023</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>340708</t>
+          <t>342020</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>382539</t>
+          <t>384318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>608138</t>
+          <t>609136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>642465</t>
+          <t>641583</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>961606</t>
+          <t>961502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1013442</t>
+          <t>1013485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,96%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132399</t>
+          <t>130620</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>174230</t>
+          <t>172918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110163</t>
+          <t>111045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144490</t>
+          <t>143492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254124</t>
+          <t>254081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>305960</t>
+          <t>306064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>696948</t>
+          <t>668716</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1137088</t>
+          <t>1137655</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1300053</t>
+          <t>1298320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1655956</t>
+          <t>1634651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2040823</t>
+          <t>1997233</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2664768</t>
+          <t>2673855</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,06%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1153239</t>
+          <t>1152672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1593379</t>
+          <t>1621611</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>581189</t>
+          <t>602494</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>937092</t>
+          <t>938825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1862704</t>
+          <t>1853617</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2486649</t>
+          <t>2530239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>314926</t>
+          <t>313567</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>369097</t>
+          <t>368055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>356948</t>
+          <t>359328</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>403544</t>
+          <t>405288</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>688570</t>
+          <t>678460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>758696</t>
+          <t>754838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,75%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277526</t>
+          <t>278568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>331697</t>
+          <t>333056</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>256919</t>
+          <t>255175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>303515</t>
+          <t>301135</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>548390</t>
+          <t>552248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>618516</t>
+          <t>628626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1341312</t>
+          <t>1311948</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1860309</t>
+          <t>1851087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2313415</t>
+          <t>2308977</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2656452</t>
+          <t>2617178</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3651006</t>
+          <t>3651235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4377187</t>
+          <t>4364087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,45%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1591580</t>
+          <t>1600802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2110577</t>
+          <t>2139941</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>993784</t>
+          <t>1033058</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1336821</t>
+          <t>1341259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2724938</t>
+          <t>2738038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3451119</t>
+          <t>3450890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/P16-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>597178</t>
+          <t>596534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>662995</t>
+          <t>660127</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>974874</t>
+          <t>972216</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1033469</t>
+          <t>1034261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1590292</t>
+          <t>1590049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1678361</t>
+          <t>1679282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>368728</t>
+          <t>371596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434545</t>
+          <t>435189</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281644</t>
+          <t>280852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>340239</t>
+          <t>342897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>668474</t>
+          <t>667553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>756543</t>
+          <t>756786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>477504</t>
+          <t>478330</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>555246</t>
+          <t>555032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>693674</t>
+          <t>695950</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>768611</t>
+          <t>775231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1194029</t>
+          <t>1189415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1301060</t>
+          <t>1303139</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1137148</t>
+          <t>1137362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1214890</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>819062</t>
+          <t>812442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>893999</t>
+          <t>891723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1979007</t>
+          <t>1976928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2086038</t>
+          <t>2090652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160663</t>
+          <t>160606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>208657</t>
+          <t>207225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>218835</t>
+          <t>219765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>264951</t>
+          <t>264612</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>394751</t>
+          <t>398387</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>459950</t>
+          <t>462779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>342751</t>
+          <t>344183</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>390745</t>
+          <t>390802</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>211461</t>
+          <t>211800</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257577</t>
+          <t>256647</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>567870</t>
+          <t>565041</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>633069</t>
+          <t>629433</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1278406</t>
+          <t>1269227</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1386547</t>
+          <t>1384329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1921725</t>
+          <t>1919943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2034112</t>
+          <t>2033055</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3225281</t>
+          <t>3227741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3389671</t>
+          <t>3384674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1888978</t>
+          <t>1891196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1997119</t>
+          <t>2006298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1345085</t>
+          <t>1346142</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1457472</t>
+          <t>1459254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3265051</t>
+          <t>3270048</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3429441</t>
+          <t>3426981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>671507</t>
+          <t>673026</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>729654</t>
+          <t>725793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1107467</t>
+          <t>1110273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1163494</t>
+          <t>1165593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1795143</t>
+          <t>1791781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1876562</t>
+          <t>1876418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244989</t>
+          <t>248850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303136</t>
+          <t>301617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173268</t>
+          <t>171169</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229295</t>
+          <t>226489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>434843</t>
+          <t>434987</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>516262</t>
+          <t>519624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>783376</t>
+          <t>780886</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>874365</t>
+          <t>877847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1046632</t>
+          <t>1049695</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1129406</t>
+          <t>1133541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1848054</t>
+          <t>1850167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1974775</t>
+          <t>1973223</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1085657</t>
+          <t>1082175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1176646</t>
+          <t>1179136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>627506</t>
+          <t>623371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>710280</t>
+          <t>707217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1742159</t>
+          <t>1743711</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1868880</t>
+          <t>1866767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172597</t>
+          <t>172706</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>220344</t>
+          <t>220326</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>244726</t>
+          <t>246335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>290156</t>
+          <t>291945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>430680</t>
+          <t>430222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>497132</t>
+          <t>499089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>259988</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307735</t>
+          <t>307626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167498</t>
+          <t>165709</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>212928</t>
+          <t>211319</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>440854</t>
+          <t>438897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>507306</t>
+          <t>507764</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1662857</t>
+          <t>1663717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1786307</t>
+          <t>1778970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2433442</t>
+          <t>2432896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2543822</t>
+          <t>2545859</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4129939</t>
+          <t>4130369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4295748</t>
+          <t>4307054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,83%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1628690</t>
+          <t>1636027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1752140</t>
+          <t>1751280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007507</t>
+          <t>1005470</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1117887</t>
+          <t>1118433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2670578</t>
+          <t>2659272</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2836387</t>
+          <t>2835957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>488256</t>
+          <t>489442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>540180</t>
+          <t>539450</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>817366</t>
+          <t>818290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>862630</t>
+          <t>865147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1318528</t>
+          <t>1321476</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1390542</t>
+          <t>1392167</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214167</t>
+          <t>214897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266091</t>
+          <t>264905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132030</t>
+          <t>129513</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>177294</t>
+          <t>176370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>358465</t>
+          <t>356840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>430479</t>
+          <t>427531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>873312</t>
+          <t>867535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>962683</t>
+          <t>962003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1101753</t>
+          <t>1100268</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1192191</t>
+          <t>1191444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2001357</t>
+          <t>2000689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2128457</t>
+          <t>2128441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1113702</t>
+          <t>1114382</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1203073</t>
+          <t>1208850</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>796109</t>
+          <t>796856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>886547</t>
+          <t>888032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1936228</t>
+          <t>1936244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2063328</t>
+          <t>2063996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221990</t>
+          <t>221119</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>271282</t>
+          <t>270870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>278616</t>
+          <t>279381</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>324989</t>
+          <t>326198</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>513069</t>
+          <t>514431</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>578269</t>
+          <t>581335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275604</t>
+          <t>276016</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324896</t>
+          <t>325767</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224151</t>
+          <t>222942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>270524</t>
+          <t>269759</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517758</t>
+          <t>514692</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>582958</t>
+          <t>581596</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1613679</t>
+          <t>1622825</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1736973</t>
+          <t>1737555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2231949</t>
+          <t>2229973</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2348766</t>
+          <t>2346123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3889010</t>
+          <t>3884330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4051138</t>
+          <t>4046399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1640645</t>
+          <t>1640063</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1763939</t>
+          <t>1754793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1183334</t>
+          <t>1185977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1300151</t>
+          <t>1302127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2858580</t>
+          <t>2863319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3020708</t>
+          <t>3025388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>362797</t>
+          <t>392347</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>342020</t>
+          <t>368546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>384318</t>
+          <t>415582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>625858</t>
+          <t>674947</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>609136</t>
+          <t>656571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>641583</t>
+          <t>693833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>988655</t>
+          <t>1067294</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>961502</t>
+          <t>1035539</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1013485</t>
+          <t>1095177</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>78,27%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>152141</t>
+          <t>186182</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130620</t>
+          <t>162947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172918</t>
+          <t>209983</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>126770</t>
+          <t>145765</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111045</t>
+          <t>126879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143492</t>
+          <t>164141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>278911</t>
+          <t>331947</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254081</t>
+          <t>304064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>306064</t>
+          <t>363702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752628</t>
+          <t>820712</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752628</t>
+          <t>820712</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752628</t>
+          <t>820712</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1267566</t>
+          <t>1399241</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1267566</t>
+          <t>1399241</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1267566</t>
+          <t>1399241</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>998908</t>
+          <t>1073055</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>668716</t>
+          <t>1017316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1137655</t>
+          <t>1126004</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1411180</t>
+          <t>1258329</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1298320</t>
+          <t>1211959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1634651</t>
+          <t>1303075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2410087</t>
+          <t>2331385</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1997233</t>
+          <t>2254193</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2673855</t>
+          <t>2400106</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1291419</t>
+          <t>1157511</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1152672</t>
+          <t>1104562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1621611</t>
+          <t>1213250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>825965</t>
+          <t>912378</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>602494</t>
+          <t>867632</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>938825</t>
+          <t>958748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2117385</t>
+          <t>2069889</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1853617</t>
+          <t>2001168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2530239</t>
+          <t>2147081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>340665</t>
+          <t>375679</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>313567</t>
+          <t>344858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>368055</t>
+          <t>403857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>381569</t>
+          <t>426671</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>359328</t>
+          <t>403042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>405288</t>
+          <t>449349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>722234</t>
+          <t>802350</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>678460</t>
+          <t>766621</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>754838</t>
+          <t>839995</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>305958</t>
+          <t>335908</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>278568</t>
+          <t>307730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>333056</t>
+          <t>366729</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>278894</t>
+          <t>308206</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>255175</t>
+          <t>285528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>301135</t>
+          <t>331835</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>584852</t>
+          <t>644114</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>552248</t>
+          <t>606469</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>628626</t>
+          <t>679843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1702370</t>
+          <t>1841082</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1311948</t>
+          <t>1778830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1851087</t>
+          <t>1904963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2418607</t>
+          <t>2359947</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2308977</t>
+          <t>2304519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2617178</t>
+          <t>2413720</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4120978</t>
+          <t>4201029</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3651235</t>
+          <t>4117241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4364087</t>
+          <t>4284165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>59,12%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1749519</t>
+          <t>1679601</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1600802</t>
+          <t>1615720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2139941</t>
+          <t>1741853</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1231629</t>
+          <t>1366350</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1033058</t>
+          <t>1312577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1341259</t>
+          <t>1421778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2981147</t>
+          <t>3045950</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2738038</t>
+          <t>2962814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3450890</t>
+          <t>3129738</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>43,19%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3650236</t>
+          <t>3726297</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3650236</t>
+          <t>3726297</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3650236</t>
+          <t>3726297</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7102125</t>
+          <t>7246979</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7102125</t>
+          <t>7246979</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7102125</t>
+          <t>7246979</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
